--- a/hardware/panel/BSN-combined-BOM.xlsx
+++ b/hardware/panel/BSN-combined-BOM.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SBA.OJ\Documents\KiCad\10.0\projects\BLE_Sensor_Node\hardware\panel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95258300-1CA6-4249-91B0-242F2E3EB41C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{529281C0-1324-4DAD-BF53-35242705266B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Combined BOM" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="201">
   <si>
     <t>BLE Sensor Node - combined BOM (BSN-C23 + BSN-N54)</t>
   </si>
@@ -615,13 +616,34 @@
   </si>
   <si>
     <t>LQW15AN6N7G8ZD</t>
+  </si>
+  <si>
+    <t>1568-18569-ND</t>
+  </si>
+  <si>
+    <t>SparkFun Electronics</t>
+  </si>
+  <si>
+    <t>315-NC191LT10-ND</t>
+  </si>
+  <si>
+    <t>Chip Quik Inc.</t>
+  </si>
+  <si>
+    <t>NC191LT10</t>
+  </si>
+  <si>
+    <t>Samsung</t>
+  </si>
+  <si>
+    <t>CL21A107MQYNNWE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -670,6 +692,23 @@
       <sz val="10"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -694,7 +733,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -717,11 +756,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -754,6 +808,24 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1059,7 +1131,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P51"/>
+  <dimension ref="A1:P53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -2307,329 +2379,319 @@
       <c r="P35" s="9"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="N36" s="14" t="s">
+      <c r="A36" s="7">
+        <v>24</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="D36" s="8">
+        <v>18569</v>
+      </c>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="9"/>
+      <c r="K36" s="7"/>
+      <c r="L36" s="7">
+        <v>1</v>
+      </c>
+      <c r="M36" s="10">
+        <v>2</v>
+      </c>
+      <c r="N36" s="11">
+        <v>19.260000000000002</v>
+      </c>
+      <c r="O36" s="12">
+        <f t="shared" ref="O36:O37" si="2">IF(OR(M36="",N36=""),"",M36*N36)</f>
+        <v>38.520000000000003</v>
+      </c>
+      <c r="P36" s="16"/>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" s="7">
+        <v>25</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="7"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="7"/>
+      <c r="L37" s="7">
+        <v>1</v>
+      </c>
+      <c r="M37" s="10">
+        <v>1</v>
+      </c>
+      <c r="N37" s="11">
+        <v>52.07</v>
+      </c>
+      <c r="O37" s="12">
+        <f t="shared" si="2"/>
+        <v>52.07</v>
+      </c>
+      <c r="P37" s="16"/>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N38" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="O36" s="15">
-        <f>SUM(O13:O35)</f>
-        <v>1120.365</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
+      <c r="O38" s="15">
+        <f>SUM(O13:O37)</f>
+        <v>1210.9549999999999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
+    <row r="42" spans="1:16" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A42" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B42" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6" t="s">
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F40" s="6" t="s">
+      <c r="F42" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G40" s="6" t="s">
+      <c r="G42" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H40" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="I40" s="6" t="s">
+      <c r="I42" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J40" s="6" t="s">
+      <c r="J42" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="K40" s="6" t="s">
+      <c r="K42" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="L40" s="6" t="s">
+      <c r="L42" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="M40" s="6" t="s">
+      <c r="M42" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="N40" s="6" t="s">
+      <c r="N42" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O40" s="6" t="s">
+      <c r="O42" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="P40" s="6" t="s">
+      <c r="P42" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" s="7">
-        <v>1</v>
-      </c>
-      <c r="B41" s="8" t="s">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A43" s="7">
+        <v>1</v>
+      </c>
+      <c r="B43" s="8" t="s">
         <v>162</v>
-      </c>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="G41" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="H41" s="9"/>
-      <c r="I41" s="7">
-        <v>0</v>
-      </c>
-      <c r="J41" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="K41" s="7">
-        <v>1</v>
-      </c>
-      <c r="L41" s="7">
-        <f t="shared" ref="L41:L48" si="2">I41*$C$5+K41*$C$6</f>
-        <v>5</v>
-      </c>
-      <c r="M41" s="10"/>
-      <c r="N41" s="11"/>
-      <c r="O41" s="12" t="str">
-        <f t="shared" ref="O41:O48" si="3">IF(OR(M41="",N41=""),"",M41*N41)</f>
-        <v/>
-      </c>
-      <c r="P41" s="9"/>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" s="7">
-        <v>2</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="H42" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="I42" s="7">
-        <v>1</v>
-      </c>
-      <c r="J42" s="9"/>
-      <c r="K42" s="7">
-        <v>0</v>
-      </c>
-      <c r="L42" s="7">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="M42" s="10"/>
-      <c r="N42" s="11"/>
-      <c r="O42" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="P42" s="9"/>
-    </row>
-    <row r="43" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A43" s="7">
-        <v>3</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>170</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
       <c r="E43" s="8" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>173</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="H43" s="9"/>
       <c r="I43" s="7">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="K43" s="7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L43" s="7">
-        <f t="shared" si="2"/>
-        <v>65</v>
+        <f t="shared" ref="L43:L50" si="3">I43*$C$5+K43*$C$6</f>
+        <v>5</v>
       </c>
       <c r="M43" s="10"/>
       <c r="N43" s="11"/>
       <c r="O43" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="O43:O50" si="4">IF(OR(M43="",N43=""),"",M43*N43)</f>
         <v/>
       </c>
       <c r="P43" s="9"/>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
       <c r="E44" s="8" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="I44" s="7">
-        <v>2</v>
-      </c>
-      <c r="J44" s="9" t="s">
-        <v>178</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J44" s="9"/>
       <c r="K44" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="7">
-        <f t="shared" si="2"/>
-        <v>15</v>
+        <f t="shared" si="3"/>
+        <v>5</v>
       </c>
       <c r="M44" s="10"/>
       <c r="N44" s="11"/>
       <c r="O44" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="P44" s="9"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A45" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
       <c r="E45" s="8" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>113</v>
+        <v>173</v>
       </c>
       <c r="I45" s="7">
-        <v>1</v>
-      </c>
-      <c r="J45" s="9"/>
+        <v>7</v>
+      </c>
+      <c r="J45" s="9" t="s">
+        <v>174</v>
+      </c>
       <c r="K45" s="7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L45" s="7">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>65</v>
       </c>
       <c r="M45" s="10"/>
       <c r="N45" s="11"/>
       <c r="O45" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="P45" s="9"/>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
       <c r="E46" s="8" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="H46" s="9"/>
+        <v>172</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>177</v>
+      </c>
       <c r="I46" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="K46" s="7">
         <v>1</v>
       </c>
       <c r="L46" s="7">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="M46" s="10"/>
       <c r="N46" s="11"/>
       <c r="O46" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="P46" s="9"/>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>186</v>
+        <v>113</v>
       </c>
       <c r="I47" s="7">
         <v>1</v>
@@ -2639,28 +2701,28 @@
         <v>0</v>
       </c>
       <c r="L47" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="M47" s="10"/>
       <c r="N47" s="11"/>
       <c r="O47" s="12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="P47" s="9"/>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
       <c r="E48" s="8" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>29</v>
@@ -2668,50 +2730,511 @@
       <c r="G48" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="H48" s="9" t="s">
-        <v>189</v>
-      </c>
+      <c r="H48" s="9"/>
       <c r="I48" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="K48" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L48" s="7">
-        <f t="shared" si="2"/>
-        <v>20</v>
+        <f t="shared" si="3"/>
+        <v>5</v>
       </c>
       <c r="M48" s="10"/>
       <c r="N48" s="11"/>
       <c r="O48" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="P48" s="9"/>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A49" s="7">
+        <v>7</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="I49" s="7">
+        <v>1</v>
+      </c>
+      <c r="J49" s="9"/>
+      <c r="K49" s="7">
+        <v>0</v>
+      </c>
+      <c r="L49" s="7">
         <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="M49" s="10"/>
+      <c r="N49" s="11"/>
+      <c r="O49" s="12" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="P48" s="9"/>
-    </row>
-    <row r="49" spans="14:15" x14ac:dyDescent="0.25">
-      <c r="N49" s="14" t="s">
+      <c r="P49" s="9"/>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A50" s="7">
+        <v>8</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="I50" s="7">
+        <v>2</v>
+      </c>
+      <c r="J50" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="K50" s="7">
+        <v>2</v>
+      </c>
+      <c r="L50" s="7">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="M50" s="10"/>
+      <c r="N50" s="11"/>
+      <c r="O50" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="P50" s="9"/>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N51" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="O49" s="15">
-        <f>SUM(O41:O48)</f>
+      <c r="O51" s="15">
+        <f>SUM(O43:O50)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="14:15" x14ac:dyDescent="0.25">
-      <c r="N51" s="14" t="s">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N53" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="O51" s="15">
-        <f>O36+O49</f>
-        <v>1120.365</v>
+      <c r="O53" s="15">
+        <f>O38+O51</f>
+        <v>1210.9549999999999</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{756C155E-0C4E-4139-8231-AE9488CE382B}">
+  <dimension ref="E12:H37"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="27.5703125" customWidth="1"/>
+    <col min="6" max="6" width="20.85546875" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="12" spans="5:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="E12" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E13" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E14" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="19">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E15" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="H15" s="19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E16" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="H16" s="19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E17" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="H17" s="19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E18" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="H18" s="19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E19" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="G19" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="H19" s="19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E20" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" s="19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E21" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="H21" s="19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E22" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="H22" s="19">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E23" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="G23" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="H23" s="19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E24" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="G24" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="H24" s="19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E25" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="H25" s="19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E26" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F26" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="G26" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="H26" s="19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E27" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="F27" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="H27" s="19">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E28" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="H28" s="19">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E29" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="F29" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="G29" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="H29" s="19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E30" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="F30" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="G30" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="H30" s="19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E31" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="F31" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="G31" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="H31" s="19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E32" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="F32" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="G32" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="H32" s="19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E33" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="F33" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="G33" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="H33" s="19">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E34" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="F34" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="G34" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="H34" s="19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E35" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="F35" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="G35" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="H35" s="19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E36" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="F36" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="G36" s="18">
+        <v>18569</v>
+      </c>
+      <c r="H36" s="19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E37" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="F37" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="G37" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="H37" s="19">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>